--- a/docs/workbook-split/dateien/KLR.xlsx
+++ b/docs/workbook-split/dateien/KLR.xlsx
@@ -728,53 +728,41 @@
       <c r="C7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7))</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7))</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7))</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7))</f>
-        <v/>
-      </c>
-      <c r="H7" s="7">
-        <f>IF(ISNUMBER(D7),D7-E7,"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="7">
-        <f>IF(ISNUMBER(D7),H7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="7">
-        <f>IF(ISNUMBER(D7),I7-G7,"")</f>
-        <v/>
-      </c>
-      <c r="K7" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7))</f>
-        <v/>
-      </c>
-      <c r="L7" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7))</f>
-        <v/>
-      </c>
-      <c r="M7" s="7">
-        <f>IF(ISNUMBER(D7),J7-K7-L7,"")</f>
-        <v/>
-      </c>
-      <c r="N7" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C7))</f>
-        <v/>
-      </c>
-      <c r="O7" s="7">
-        <f>IF(ISNUMBER(D7),M7-N7,"")</f>
-        <v/>
+      <c r="D7" s="6" t="n">
+        <v>1918210.96</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1084847.47</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>796.87</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>833363.49</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>832566.62</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>832566.62</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>-57065.09</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>50356.1</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>839275.61</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>9921.48</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>829354.13</v>
       </c>
       <c r="P7" s="1" t="n"/>
       <c r="Q7" s="1" t="n"/>
@@ -786,53 +774,41 @@
       <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8))</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8))</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8))</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8))</f>
-        <v/>
-      </c>
-      <c r="H8" s="7">
-        <f>IF(ISNUMBER(D8),D8-E8,"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="7">
-        <f>IF(ISNUMBER(D8),H8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="7">
-        <f>IF(ISNUMBER(D8),I8-G8,"")</f>
-        <v/>
-      </c>
-      <c r="K8" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8))</f>
-        <v/>
-      </c>
-      <c r="L8" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8))</f>
-        <v/>
-      </c>
-      <c r="M8" s="7">
-        <f>IF(ISNUMBER(D8),J8-K8-L8,"")</f>
-        <v/>
-      </c>
-      <c r="N8" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C8))</f>
-        <v/>
-      </c>
-      <c r="O8" s="7">
-        <f>IF(ISNUMBER(D8),M8-N8,"")</f>
-        <v/>
+      <c r="D8" s="6" t="n">
+        <v>2577067.73</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1730963.89</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>7075.12</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>846103.8400000001</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>839028.7200000001</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>839028.7200000001</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-176284.77</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>52795.58</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>962517.9100000001</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>22920.79</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>939597.1200000001</v>
       </c>
       <c r="P8" s="1" t="n"/>
       <c r="Q8" s="1" t="n"/>
@@ -844,53 +820,41 @@
       <c r="C9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9))</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9))</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9))</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9))</f>
-        <v/>
-      </c>
-      <c r="H9" s="7">
-        <f>IF(ISNUMBER(D9),D9-E9,"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="7">
-        <f>IF(ISNUMBER(D9),H9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="7">
-        <f>IF(ISNUMBER(D9),I9-G9,"")</f>
-        <v/>
-      </c>
-      <c r="K9" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9))</f>
-        <v/>
-      </c>
-      <c r="L9" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9))</f>
-        <v/>
-      </c>
-      <c r="M9" s="7">
-        <f>IF(ISNUMBER(D9),J9-K9-L9,"")</f>
-        <v/>
-      </c>
-      <c r="N9" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C9))</f>
-        <v/>
-      </c>
-      <c r="O9" s="7">
-        <f>IF(ISNUMBER(D9),M9-N9,"")</f>
-        <v/>
+      <c r="D9" s="6" t="n">
+        <v>2407542.34</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1767771.17</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>3015.13</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>639771.1699999999</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>636756.0399999999</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>636756.0399999999</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>-152656.94</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>80518.91</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>708894.0699999999</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>45401.35</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>663492.72</v>
       </c>
       <c r="P9" s="1" t="n"/>
       <c r="Q9" s="1" t="n"/>
@@ -902,53 +866,41 @@
       <c r="C10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10))</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10))</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10))</f>
-        <v/>
-      </c>
-      <c r="H10" s="7">
-        <f>IF(ISNUMBER(D10),D10-E10,"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="7">
-        <f>IF(ISNUMBER(D10),H10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="7">
-        <f>IF(ISNUMBER(D10),I10-G10,"")</f>
-        <v/>
-      </c>
-      <c r="K10" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10))</f>
-        <v/>
-      </c>
-      <c r="L10" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10))</f>
-        <v/>
-      </c>
-      <c r="M10" s="7">
-        <f>IF(ISNUMBER(D10),J10-K10-L10,"")</f>
-        <v/>
-      </c>
-      <c r="N10" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C10))</f>
-        <v/>
-      </c>
-      <c r="O10" s="7">
-        <f>IF(ISNUMBER(D10),M10-N10,"")</f>
-        <v/>
+      <c r="D10" s="6" t="n">
+        <v>1934642.03</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1525433.97</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>4695.74</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>409208.0600000001</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>404512.3200000001</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>404512.3200000001</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>-176440.83</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>80089.74000000001</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>500863.41</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>-21060.8</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>521924.21</v>
       </c>
       <c r="P10" s="1" t="n"/>
       <c r="Q10" s="1" t="n"/>
@@ -960,53 +912,41 @@
       <c r="C11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11))</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11))</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11))</f>
-        <v/>
-      </c>
-      <c r="H11" s="7">
-        <f>IF(ISNUMBER(D11),D11-E11,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="7">
-        <f>IF(ISNUMBER(D11),H11-F11,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="7">
-        <f>IF(ISNUMBER(D11),I11-G11,"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11))</f>
-        <v/>
-      </c>
-      <c r="L11" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11))</f>
-        <v/>
-      </c>
-      <c r="M11" s="7">
-        <f>IF(ISNUMBER(D11),J11-K11-L11,"")</f>
-        <v/>
-      </c>
-      <c r="N11" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C11))</f>
-        <v/>
-      </c>
-      <c r="O11" s="7">
-        <f>IF(ISNUMBER(D11),M11-N11,"")</f>
-        <v/>
+      <c r="D11" s="6" t="n">
+        <v>1088379.51</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>591663.62</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>2428.23</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>496715.89</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>494287.66</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>494287.66</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>-29199.96</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>61602.01</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>461885.61</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>32230.59</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>429655.02</v>
       </c>
       <c r="P11" s="1" t="n"/>
       <c r="Q11" s="1" t="n"/>
@@ -1018,53 +958,41 @@
       <c r="C12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12))</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12))</f>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12))</f>
-        <v/>
-      </c>
-      <c r="H12" s="7">
-        <f>IF(ISNUMBER(D12),D12-E12,"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="7">
-        <f>IF(ISNUMBER(D12),H12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="7">
-        <f>IF(ISNUMBER(D12),I12-G12,"")</f>
-        <v/>
-      </c>
-      <c r="K12" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12))</f>
-        <v/>
-      </c>
-      <c r="L12" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12))</f>
-        <v/>
-      </c>
-      <c r="M12" s="7">
-        <f>IF(ISNUMBER(D12),J12-K12-L12,"")</f>
-        <v/>
-      </c>
-      <c r="N12" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C12))</f>
-        <v/>
-      </c>
-      <c r="O12" s="7">
-        <f>IF(ISNUMBER(D12),M12-N12,"")</f>
-        <v/>
+      <c r="D12" s="6" t="n">
+        <v>2780738.46</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>2119489.65</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>24361.48</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>661248.8100000001</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>636887.3300000001</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>636887.3300000001</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-137629.16</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>67124.73</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>707391.7600000001</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>30367.14</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>677024.6200000001</v>
       </c>
       <c r="P12" s="1" t="n"/>
       <c r="Q12" s="1" t="n"/>
@@ -1076,53 +1004,41 @@
       <c r="C13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13))</f>
-        <v/>
-      </c>
-      <c r="E13" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13))</f>
-        <v/>
-      </c>
-      <c r="F13" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13))</f>
-        <v/>
-      </c>
-      <c r="H13" s="7">
-        <f>IF(ISNUMBER(D13),D13-E13,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="7">
-        <f>IF(ISNUMBER(D13),H13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="7">
-        <f>IF(ISNUMBER(D13),I13-G13,"")</f>
-        <v/>
-      </c>
-      <c r="K13" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13))</f>
-        <v/>
-      </c>
-      <c r="L13" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13))</f>
-        <v/>
-      </c>
-      <c r="M13" s="7">
-        <f>IF(ISNUMBER(D13),J13-K13-L13,"")</f>
-        <v/>
-      </c>
-      <c r="N13" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C13))</f>
-        <v/>
-      </c>
-      <c r="O13" s="7">
-        <f>IF(ISNUMBER(D13),M13-N13,"")</f>
-        <v/>
+      <c r="D13" s="6" t="n">
+        <v>1615953.83</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1532184.2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2493.62</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>83769.63000000012</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>81276.01000000013</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>81276.01000000013</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>-94946.12</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>61244.52</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>114977.6100000001</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>22212.3</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>92765.31000000013</v>
       </c>
       <c r="P13" s="1" t="n"/>
       <c r="Q13" s="1" t="n"/>
@@ -1134,53 +1050,41 @@
       <c r="C14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14))</f>
-        <v/>
-      </c>
-      <c r="E14" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14))</f>
-        <v/>
-      </c>
-      <c r="F14" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14))</f>
-        <v/>
-      </c>
-      <c r="H14" s="7">
-        <f>IF(ISNUMBER(D14),D14-E14,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="7">
-        <f>IF(ISNUMBER(D14),H14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="7">
-        <f>IF(ISNUMBER(D14),I14-G14,"")</f>
-        <v/>
-      </c>
-      <c r="K14" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14))</f>
-        <v/>
-      </c>
-      <c r="L14" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14))</f>
-        <v/>
-      </c>
-      <c r="M14" s="7">
-        <f>IF(ISNUMBER(D14),J14-K14-L14,"")</f>
-        <v/>
-      </c>
-      <c r="N14" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C14))</f>
-        <v/>
-      </c>
-      <c r="O14" s="7">
-        <f>IF(ISNUMBER(D14),M14-N14,"")</f>
-        <v/>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>247016.5</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>148296.89</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>-247016.5</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>-247016.5</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>-395313.39</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>-111684.33</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>59143.57</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>-342772.63</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>51584.81</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>-394357.44</v>
       </c>
       <c r="P14" s="1" t="n"/>
       <c r="Q14" s="1" t="n"/>
@@ -1192,53 +1096,41 @@
       <c r="C15" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15))</f>
-        <v/>
-      </c>
-      <c r="E15" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15))</f>
-        <v/>
-      </c>
-      <c r="F15" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15))</f>
-        <v/>
-      </c>
-      <c r="G15" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15))</f>
-        <v/>
-      </c>
-      <c r="H15" s="7">
-        <f>IF(ISNUMBER(D15),D15-E15,"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="7">
-        <f>IF(ISNUMBER(D15),H15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="7">
-        <f>IF(ISNUMBER(D15),I15-G15,"")</f>
-        <v/>
-      </c>
-      <c r="K15" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15))</f>
-        <v/>
-      </c>
-      <c r="L15" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15))</f>
-        <v/>
-      </c>
-      <c r="M15" s="7">
-        <f>IF(ISNUMBER(D15),J15-K15-L15,"")</f>
-        <v/>
-      </c>
-      <c r="N15" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C15))</f>
-        <v/>
-      </c>
-      <c r="O15" s="7">
-        <f>IF(ISNUMBER(D15),M15-N15,"")</f>
-        <v/>
+      <c r="D15" s="6" t="n">
+        <v>887356.29</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1762216.69</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>18620.03</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>-874860.3999999999</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>-893480.4299999999</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>-893480.4299999999</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>66065.95</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>54298.21</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>-1013844.59</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>-320317.63</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>-693526.9599999998</v>
       </c>
       <c r="P15" s="1" t="n"/>
       <c r="Q15" s="1" t="n"/>
@@ -1250,54 +1142,18 @@
       <c r="C16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16))</f>
-        <v/>
-      </c>
-      <c r="E16" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16))</f>
-        <v/>
-      </c>
-      <c r="F16" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16))</f>
-        <v/>
-      </c>
-      <c r="H16" s="7">
-        <f>IF(ISNUMBER(D16),D16-E16,"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="7">
-        <f>IF(ISNUMBER(D16),H16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="7">
-        <f>IF(ISNUMBER(D16),I16-G16,"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16))</f>
-        <v/>
-      </c>
-      <c r="L16" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16))</f>
-        <v/>
-      </c>
-      <c r="M16" s="7">
-        <f>IF(ISNUMBER(D16),J16-K16-L16,"")</f>
-        <v/>
-      </c>
-      <c r="N16" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C16))</f>
-        <v/>
-      </c>
-      <c r="O16" s="7">
-        <f>IF(ISNUMBER(D16),M16-N16,"")</f>
-        <v/>
-      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="7" t="n"/>
       <c r="P16" s="1" t="n"/>
       <c r="Q16" s="1" t="n"/>
       <c r="R16" s="1" t="n"/>
@@ -1308,54 +1164,18 @@
       <c r="C17" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D17" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17))</f>
-        <v/>
-      </c>
-      <c r="E17" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17))</f>
-        <v/>
-      </c>
-      <c r="F17" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17))</f>
-        <v/>
-      </c>
-      <c r="G17" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17))</f>
-        <v/>
-      </c>
-      <c r="H17" s="7">
-        <f>IF(ISNUMBER(D17),D17-E17,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="7">
-        <f>IF(ISNUMBER(D17),H17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="7">
-        <f>IF(ISNUMBER(D17),I17-G17,"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17))</f>
-        <v/>
-      </c>
-      <c r="L17" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17))</f>
-        <v/>
-      </c>
-      <c r="M17" s="7">
-        <f>IF(ISNUMBER(D17),J17-K17-L17,"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C17))</f>
-        <v/>
-      </c>
-      <c r="O17" s="7">
-        <f>IF(ISNUMBER(D17),M17-N17,"")</f>
-        <v/>
-      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="7" t="n"/>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="7" t="n"/>
       <c r="P17" s="1" t="n"/>
       <c r="Q17" s="1" t="n"/>
       <c r="R17" s="1" t="n"/>
@@ -1366,54 +1186,18 @@
       <c r="C18" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D18" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$C$8:$C$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18))</f>
-        <v/>
-      </c>
-      <c r="E18" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$D$8:$D$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18))</f>
-        <v/>
-      </c>
-      <c r="F18" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$E$8:$E$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18))</f>
-        <v/>
-      </c>
-      <c r="G18" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$F$8:$F$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18))</f>
-        <v/>
-      </c>
-      <c r="H18" s="7">
-        <f>IF(ISNUMBER(D18),D18-E18,"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="7">
-        <f>IF(ISNUMBER(D18),H18-F18,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="7">
-        <f>IF(ISNUMBER(D18),I18-G18,"")</f>
-        <v/>
-      </c>
-      <c r="K18" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$I$8:$I$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18))</f>
-        <v/>
-      </c>
-      <c r="L18" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$L$8:$L$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18))</f>
-        <v/>
-      </c>
-      <c r="M18" s="7">
-        <f>IF(ISNUMBER(D18),J18-K18-L18,"")</f>
-        <v/>
-      </c>
-      <c r="N18" s="6">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18)=0,"",SUMIFS('[D KLR.xlsx]D KLR'!$M$8:$M$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,C18))</f>
-        <v/>
-      </c>
-      <c r="O18" s="7">
-        <f>IF(ISNUMBER(D18),M18-N18,"")</f>
-        <v/>
-      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="7" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="7" t="n"/>
       <c r="P18" s="1" t="n"/>
       <c r="Q18" s="1" t="n"/>
       <c r="R18" s="1" t="n"/>
@@ -1446,53 +1230,41 @@
           <t>YTD</t>
         </is>
       </c>
-      <c r="D20" s="9">
-        <f>SUMIFS(D7:D18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E20" s="9">
-        <f>SUMIFS(E7:E18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="F20" s="9">
-        <f>SUMIFS(F7:F18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="G20" s="9">
-        <f>SUMIFS(G7:G18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="H20" s="9">
-        <f>SUMIFS(H7:H18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="I20" s="9">
-        <f>SUMIFS(I7:I18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="J20" s="9">
-        <f>SUMIFS(J7:J18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="K20" s="9">
-        <f>SUMIFS(K7:K18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="L20" s="9">
-        <f>SUMIFS(L7:L18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="M20" s="9">
-        <f>SUMIFS(M7:M18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="N20" s="9">
-        <f>SUMIFS(N7:N18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="O20" s="9">
-        <f>SUMIFS(O7:O18,$C$7:$C$18,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
+      <c r="D20" s="9" t="n">
+        <v>15209891.15</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>12361587.16</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>63486.22</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>148296.89</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>2848303.990000001</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>2784817.77</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>2636520.880000001</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>-869841.25</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>567173.37</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>2939188.760000001</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>-126739.97</v>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>3065928.73</v>
       </c>
       <c r="P20" s="1" t="n"/>
       <c r="Q20" s="1" t="n"/>
@@ -1658,13 +1430,11 @@
       <c r="F27" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G27" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C27)</f>
-        <v/>
+      <c r="G27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I27" s="1" t="n"/>
       <c r="J27" s="1" t="n"/>
@@ -1698,13 +1468,11 @@
       <c r="F28" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C28)</f>
-        <v/>
+      <c r="G28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I28" s="1" t="n"/>
       <c r="J28" s="1" t="n"/>
@@ -1738,13 +1506,11 @@
       <c r="F29" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C29)</f>
-        <v/>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I29" s="1" t="n"/>
       <c r="J29" s="1" t="n"/>
@@ -1778,13 +1544,11 @@
       <c r="F30" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C30)</f>
-        <v/>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I30" s="1" t="n"/>
       <c r="J30" s="1" t="n"/>
@@ -1818,13 +1582,11 @@
       <c r="F31" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C31)</f>
-        <v/>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I31" s="1" t="n"/>
       <c r="J31" s="1" t="n"/>
@@ -1858,13 +1620,11 @@
       <c r="F32" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C32)</f>
-        <v/>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I32" s="1" t="n"/>
       <c r="J32" s="1" t="n"/>
@@ -1898,13 +1658,11 @@
       <c r="F33" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C33)</f>
-        <v/>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I33" s="1" t="n"/>
       <c r="J33" s="1" t="n"/>
@@ -1938,13 +1696,11 @@
       <c r="F34" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G34" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C34)</f>
-        <v/>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I34" s="1" t="n"/>
       <c r="J34" s="1" t="n"/>
@@ -1978,13 +1734,11 @@
       <c r="F35" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G35" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C35)</f>
-        <v/>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I35" s="1" t="n"/>
       <c r="J35" s="1" t="n"/>
@@ -2018,13 +1772,11 @@
       <c r="F36" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G36" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C36)</f>
-        <v/>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I36" s="1" t="n"/>
       <c r="J36" s="1" t="n"/>
@@ -2058,13 +1810,11 @@
       <c r="F37" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G37" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C37)</f>
-        <v/>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I37" s="1" t="n"/>
       <c r="J37" s="1" t="n"/>
@@ -2098,13 +1848,11 @@
       <c r="F38" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G38" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C38)</f>
-        <v/>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I38" s="1" t="n"/>
       <c r="J38" s="1" t="n"/>
@@ -2138,13 +1886,11 @@
       <c r="F39" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G39" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C39)</f>
-        <v/>
-      </c>
-      <c r="H39" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C39)</f>
-        <v/>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I39" s="1" t="n"/>
       <c r="J39" s="1" t="n"/>
@@ -2178,13 +1924,11 @@
       <c r="F40" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G40" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C40)</f>
-        <v/>
-      </c>
-      <c r="H40" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C40)</f>
-        <v/>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I40" s="1" t="n"/>
       <c r="J40" s="1" t="n"/>
@@ -2218,13 +1962,11 @@
       <c r="F41" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G41" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C41)</f>
-        <v/>
-      </c>
-      <c r="H41" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C41)</f>
-        <v/>
+      <c r="G41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I41" s="1" t="n"/>
       <c r="J41" s="1" t="n"/>
@@ -2258,13 +2000,11 @@
       <c r="F42" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G42" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C42)</f>
-        <v/>
-      </c>
-      <c r="H42" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C42)</f>
-        <v/>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I42" s="1" t="n"/>
       <c r="J42" s="1" t="n"/>
@@ -2298,13 +2038,11 @@
       <c r="F43" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G43" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C43)</f>
-        <v/>
-      </c>
-      <c r="H43" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C43)</f>
-        <v/>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I43" s="1" t="n"/>
       <c r="J43" s="1" t="n"/>
@@ -2338,13 +2076,11 @@
       <c r="F44" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G44" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C44)</f>
-        <v/>
-      </c>
-      <c r="H44" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C44)</f>
-        <v/>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I44" s="1" t="n"/>
       <c r="J44" s="1" t="n"/>
@@ -2378,13 +2114,11 @@
       <c r="F45" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G45" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C45)</f>
-        <v/>
-      </c>
-      <c r="H45" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C45)</f>
-        <v/>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I45" s="1" t="n"/>
       <c r="J45" s="1" t="n"/>
@@ -2418,13 +2152,11 @@
       <c r="F46" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G46" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C46)</f>
-        <v/>
-      </c>
-      <c r="H46" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C46)</f>
-        <v/>
+      <c r="G46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I46" s="1" t="n"/>
       <c r="J46" s="1" t="n"/>
@@ -2458,13 +2190,11 @@
       <c r="F47" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C47)</f>
-        <v/>
-      </c>
-      <c r="H47" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C47)</f>
-        <v/>
+      <c r="G47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I47" s="1" t="n"/>
       <c r="J47" s="1" t="n"/>
@@ -2498,13 +2228,11 @@
       <c r="F48" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C48)</f>
-        <v/>
-      </c>
-      <c r="H48" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C48)</f>
-        <v/>
+      <c r="G48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I48" s="1" t="n"/>
       <c r="J48" s="1" t="n"/>
@@ -2538,13 +2266,11 @@
       <c r="F49" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G49" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C49)</f>
-        <v/>
-      </c>
-      <c r="H49" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C49)</f>
-        <v/>
+      <c r="G49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I49" s="1" t="n"/>
       <c r="J49" s="1" t="n"/>
@@ -2578,13 +2304,11 @@
       <c r="F50" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G50" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C50)</f>
-        <v/>
-      </c>
-      <c r="H50" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C50)</f>
-        <v/>
+      <c r="G50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I50" s="1" t="n"/>
       <c r="J50" s="1" t="n"/>
@@ -2618,13 +2342,11 @@
       <c r="F51" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C51)</f>
-        <v/>
-      </c>
-      <c r="H51" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C51)</f>
-        <v/>
+      <c r="G51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I51" s="1" t="n"/>
       <c r="J51" s="1" t="n"/>
@@ -2658,13 +2380,11 @@
       <c r="F52" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C52)</f>
-        <v/>
-      </c>
-      <c r="H52" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C52)</f>
-        <v/>
+      <c r="G52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I52" s="1" t="n"/>
       <c r="J52" s="1" t="n"/>
@@ -2698,13 +2418,11 @@
       <c r="F53" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G53" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C53)</f>
-        <v/>
-      </c>
-      <c r="H53" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C53)</f>
-        <v/>
+      <c r="G53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I53" s="1" t="n"/>
       <c r="J53" s="1" t="n"/>
@@ -2738,13 +2456,11 @@
       <c r="F54" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G54" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C54)</f>
-        <v/>
-      </c>
-      <c r="H54" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C54)</f>
-        <v/>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I54" s="1" t="n"/>
       <c r="J54" s="1" t="n"/>
@@ -2778,13 +2494,11 @@
       <c r="F55" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G55" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C55)</f>
-        <v/>
-      </c>
-      <c r="H55" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C55)</f>
-        <v/>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I55" s="1" t="n"/>
       <c r="J55" s="1" t="n"/>
@@ -2818,13 +2532,11 @@
       <c r="F56" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G56" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C56)</f>
-        <v/>
-      </c>
-      <c r="H56" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C56)</f>
-        <v/>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I56" s="1" t="n"/>
       <c r="J56" s="1" t="n"/>
@@ -2858,13 +2570,11 @@
       <c r="F57" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C57)</f>
-        <v/>
-      </c>
-      <c r="H57" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C57)</f>
-        <v/>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I57" s="1" t="n"/>
       <c r="J57" s="1" t="n"/>
@@ -2898,13 +2608,11 @@
       <c r="F58" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G58" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C58)</f>
-        <v/>
-      </c>
-      <c r="H58" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C58)</f>
-        <v/>
+      <c r="G58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I58" s="1" t="n"/>
       <c r="J58" s="1" t="n"/>
@@ -2938,13 +2646,11 @@
       <c r="F59" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C59)</f>
-        <v/>
-      </c>
-      <c r="H59" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C59)</f>
-        <v/>
+      <c r="G59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I59" s="1" t="n"/>
       <c r="J59" s="1" t="n"/>
@@ -2978,13 +2684,11 @@
       <c r="F60" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="G60" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C60)</f>
-        <v/>
-      </c>
-      <c r="H60" s="11">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C60)</f>
-        <v/>
+      <c r="G60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="I60" s="1" t="n"/>
       <c r="J60" s="1" t="n"/>
@@ -3016,13 +2720,11 @@
       <c r="F61" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G61" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C61)</f>
-        <v/>
-      </c>
-      <c r="H61" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C61)</f>
-        <v/>
+      <c r="G61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3044,13 +2746,11 @@
       <c r="F62" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G62" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C62)</f>
-        <v/>
-      </c>
-      <c r="H62" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C62)</f>
-        <v/>
+      <c r="G62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3072,13 +2772,11 @@
       <c r="F63" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G63" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C63)</f>
-        <v/>
-      </c>
-      <c r="H63" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C63)</f>
-        <v/>
+      <c r="G63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3100,13 +2798,11 @@
       <c r="F64" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G64" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C64)</f>
-        <v/>
-      </c>
-      <c r="H64" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C64)</f>
-        <v/>
+      <c r="G64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3128,13 +2824,11 @@
       <c r="F65" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G65" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C65)</f>
-        <v/>
-      </c>
-      <c r="H65" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C65)</f>
-        <v/>
+      <c r="G65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3156,13 +2850,11 @@
       <c r="F66" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G66" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C66)</f>
-        <v/>
-      </c>
-      <c r="H66" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C66)</f>
-        <v/>
+      <c r="G66" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3184,13 +2876,11 @@
       <c r="F67" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C67)</f>
-        <v/>
-      </c>
-      <c r="H67" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C67)</f>
-        <v/>
+      <c r="G67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3212,13 +2902,11 @@
       <c r="F68" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G68" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C68)</f>
-        <v/>
-      </c>
-      <c r="H68" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C68)</f>
-        <v/>
+      <c r="G68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3240,13 +2928,11 @@
       <c r="F69" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G69" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C69)</f>
-        <v/>
-      </c>
-      <c r="H69" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C69)</f>
-        <v/>
+      <c r="G69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3268,13 +2954,11 @@
       <c r="F70" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G70" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C70)</f>
-        <v/>
-      </c>
-      <c r="H70" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C70)</f>
-        <v/>
+      <c r="G70" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3296,13 +2980,11 @@
       <c r="F71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G71" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C71)</f>
-        <v/>
-      </c>
-      <c r="H71" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C71)</f>
-        <v/>
+      <c r="G71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3324,13 +3006,11 @@
       <c r="F72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C72)</f>
-        <v/>
-      </c>
-      <c r="H72" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C72)</f>
-        <v/>
+      <c r="G72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3352,13 +3032,11 @@
       <c r="F73" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C73)</f>
-        <v/>
-      </c>
-      <c r="H73" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C73)</f>
-        <v/>
+      <c r="G73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3380,13 +3058,11 @@
       <c r="F74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G74" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C74)</f>
-        <v/>
-      </c>
-      <c r="H74" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C74)</f>
-        <v/>
+      <c r="G74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3408,13 +3084,11 @@
       <c r="F75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C75)</f>
-        <v/>
-      </c>
-      <c r="H75" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C75)</f>
-        <v/>
+      <c r="G75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3436,13 +3110,11 @@
       <c r="F76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C76)</f>
-        <v/>
-      </c>
-      <c r="H76" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C76)</f>
-        <v/>
+      <c r="G76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3464,13 +3136,11 @@
       <c r="F77" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G77" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C77)</f>
-        <v/>
-      </c>
-      <c r="H77" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C77)</f>
-        <v/>
+      <c r="G77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -3492,13 +3162,11 @@
       <c r="F78" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G78" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C78)</f>
-        <v/>
-      </c>
-      <c r="H78" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C78)</f>
-        <v/>
+      <c r="G78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -3520,13 +3188,11 @@
       <c r="F79" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G79" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C79)</f>
-        <v/>
-      </c>
-      <c r="H79" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C79)</f>
-        <v/>
+      <c r="G79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -3548,13 +3214,11 @@
       <c r="F80" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G80" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C80)</f>
-        <v/>
-      </c>
-      <c r="H80" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C80)</f>
-        <v/>
+      <c r="G80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -3576,13 +3240,11 @@
       <c r="F81" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G81" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C81)</f>
-        <v/>
-      </c>
-      <c r="H81" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C81)</f>
-        <v/>
+      <c r="G81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -3604,13 +3266,11 @@
       <c r="F82" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G82" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C82)</f>
-        <v/>
-      </c>
-      <c r="H82" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C82)</f>
-        <v/>
+      <c r="G82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -3632,13 +3292,11 @@
       <c r="F83" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G83" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C83)</f>
-        <v/>
-      </c>
-      <c r="H83" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C83)</f>
-        <v/>
+      <c r="G83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -3660,13 +3318,11 @@
       <c r="F84" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G84" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C84)</f>
-        <v/>
-      </c>
-      <c r="H84" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C84)</f>
-        <v/>
+      <c r="G84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -3688,13 +3344,11 @@
       <c r="F85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G85" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C85)</f>
-        <v/>
-      </c>
-      <c r="H85" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C85)</f>
-        <v/>
+      <c r="G85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -3716,13 +3370,11 @@
       <c r="F86" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G86" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C86)</f>
-        <v/>
-      </c>
-      <c r="H86" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C86)</f>
-        <v/>
+      <c r="G86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -3744,13 +3396,11 @@
       <c r="F87" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G87" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C87)</f>
-        <v/>
-      </c>
-      <c r="H87" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C87)</f>
-        <v/>
+      <c r="G87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -3772,13 +3422,11 @@
       <c r="F88" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G88" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C88)</f>
-        <v/>
-      </c>
-      <c r="H88" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C88)</f>
-        <v/>
+      <c r="G88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -3800,13 +3448,11 @@
       <c r="F89" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G89" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C89)</f>
-        <v/>
-      </c>
-      <c r="H89" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C89)</f>
-        <v/>
+      <c r="G89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -3828,13 +3474,11 @@
       <c r="F90" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G90" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C90)</f>
-        <v/>
-      </c>
-      <c r="H90" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C90)</f>
-        <v/>
+      <c r="G90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -3856,13 +3500,11 @@
       <c r="F91" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G91" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C91)</f>
-        <v/>
-      </c>
-      <c r="H91" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C91)</f>
-        <v/>
+      <c r="G91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -3884,13 +3526,11 @@
       <c r="F92" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G92" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C92)</f>
-        <v/>
-      </c>
-      <c r="H92" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C92)</f>
-        <v/>
+      <c r="G92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -3912,13 +3552,11 @@
       <c r="F93" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G93" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C93)</f>
-        <v/>
-      </c>
-      <c r="H93" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C93)</f>
-        <v/>
+      <c r="G93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -3940,13 +3578,11 @@
       <c r="F94" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G94" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C94)</f>
-        <v/>
-      </c>
-      <c r="H94" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C94)</f>
-        <v/>
+      <c r="G94" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -3968,13 +3604,11 @@
       <c r="F95" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G95" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C95)</f>
-        <v/>
-      </c>
-      <c r="H95" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C95)</f>
-        <v/>
+      <c r="G95" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -3996,13 +3630,11 @@
       <c r="F96" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G96" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C96)</f>
-        <v/>
-      </c>
-      <c r="H96" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C96)</f>
-        <v/>
+      <c r="G96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
@@ -4024,13 +3656,11 @@
       <c r="F97" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G97" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C97)</f>
-        <v/>
-      </c>
-      <c r="H97" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C97)</f>
-        <v/>
+      <c r="G97" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98" ht="21" customHeight="1">
@@ -4052,13 +3682,11 @@
       <c r="F98" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G98" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C98)</f>
-        <v/>
-      </c>
-      <c r="H98" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C98)</f>
-        <v/>
+      <c r="G98" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99" ht="21" customHeight="1">
@@ -4080,13 +3708,11 @@
       <c r="F99" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G99" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C99)</f>
-        <v/>
-      </c>
-      <c r="H99" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C99)</f>
-        <v/>
+      <c r="G99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100" ht="21" customHeight="1">
@@ -4108,13 +3734,11 @@
       <c r="F100" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G100" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C100)</f>
-        <v/>
-      </c>
-      <c r="H100" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C100)</f>
-        <v/>
+      <c r="G100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101" ht="21" customHeight="1">
@@ -4136,13 +3760,11 @@
       <c r="F101" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G101" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C101)</f>
-        <v/>
-      </c>
-      <c r="H101" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C101)</f>
-        <v/>
+      <c r="G101" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102" ht="21" customHeight="1">
@@ -4164,13 +3786,11 @@
       <c r="F102" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G102" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C102)</f>
-        <v/>
-      </c>
-      <c r="H102" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C102)</f>
-        <v/>
+      <c r="G102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103" ht="21" customHeight="1">
@@ -4192,13 +3812,11 @@
       <c r="F103" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G103" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C103)</f>
-        <v/>
-      </c>
-      <c r="H103" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C103)</f>
-        <v/>
+      <c r="G103" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104" ht="21" customHeight="1">
@@ -4220,13 +3838,11 @@
       <c r="F104" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G104" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C104)</f>
-        <v/>
-      </c>
-      <c r="H104" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C104)</f>
-        <v/>
+      <c r="G104" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105" ht="21" customHeight="1">
@@ -4248,13 +3864,11 @@
       <c r="F105" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G105" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C105)</f>
-        <v/>
-      </c>
-      <c r="H105" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C105)</f>
-        <v/>
+      <c r="G105" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106" ht="21" customHeight="1">
@@ -4276,13 +3890,11 @@
       <c r="F106" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G106" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C106)</f>
-        <v/>
-      </c>
-      <c r="H106" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C106)</f>
-        <v/>
+      <c r="G106" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="21" customHeight="1">
@@ -4304,13 +3916,11 @@
       <c r="F107" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G107" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C107)</f>
-        <v/>
-      </c>
-      <c r="H107" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C107)</f>
-        <v/>
+      <c r="G107" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108" ht="21" customHeight="1">
@@ -4332,13 +3942,11 @@
       <c r="F108" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G108" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C108)</f>
-        <v/>
-      </c>
-      <c r="H108" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C108)</f>
-        <v/>
+      <c r="G108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109" ht="21" customHeight="1">
@@ -4360,13 +3968,11 @@
       <c r="F109" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G109" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C109)</f>
-        <v/>
-      </c>
-      <c r="H109" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C109)</f>
-        <v/>
+      <c r="G109" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110" ht="21" customHeight="1">
@@ -4388,13 +3994,11 @@
       <c r="F110" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G110" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C110)</f>
-        <v/>
-      </c>
-      <c r="H110" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C110)</f>
-        <v/>
+      <c r="G110" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111" ht="21" customHeight="1">
@@ -4416,13 +4020,11 @@
       <c r="F111" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G111" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C111)</f>
-        <v/>
-      </c>
-      <c r="H111" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C111)</f>
-        <v/>
+      <c r="G111" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112" ht="21" customHeight="1">
@@ -4444,13 +4046,11 @@
       <c r="F112" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G112" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C112)</f>
-        <v/>
-      </c>
-      <c r="H112" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C112)</f>
-        <v/>
+      <c r="G112" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113" ht="21" customHeight="1">
@@ -4472,13 +4072,11 @@
       <c r="F113" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G113" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C113)</f>
-        <v/>
-      </c>
-      <c r="H113" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C113)</f>
-        <v/>
+      <c r="G113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114" ht="21" customHeight="1">
@@ -4500,13 +4098,11 @@
       <c r="F114" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G114" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C114)</f>
-        <v/>
-      </c>
-      <c r="H114" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C114)</f>
-        <v/>
+      <c r="G114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115" ht="21" customHeight="1">
@@ -4528,13 +4124,11 @@
       <c r="F115" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G115" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C115)</f>
-        <v/>
-      </c>
-      <c r="H115" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C115)</f>
-        <v/>
+      <c r="G115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116" ht="21" customHeight="1">
@@ -4556,13 +4150,11 @@
       <c r="F116" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G116" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C116)</f>
-        <v/>
-      </c>
-      <c r="H116" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C116)</f>
-        <v/>
+      <c r="G116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117" ht="21" customHeight="1">
@@ -4584,13 +4176,11 @@
       <c r="F117" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G117" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C117)</f>
-        <v/>
-      </c>
-      <c r="H117" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C117)</f>
-        <v/>
+      <c r="G117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118" ht="21" customHeight="1">
@@ -4612,13 +4202,11 @@
       <c r="F118" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G118" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C118)</f>
-        <v/>
-      </c>
-      <c r="H118" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C118)</f>
-        <v/>
+      <c r="G118" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119" ht="21" customHeight="1">
@@ -4640,13 +4228,11 @@
       <c r="F119" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G119" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C119)</f>
-        <v/>
-      </c>
-      <c r="H119" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C119)</f>
-        <v/>
+      <c r="G119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120" ht="21" customHeight="1">
@@ -4668,13 +4254,11 @@
       <c r="F120" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G120" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C120)</f>
-        <v/>
-      </c>
-      <c r="H120" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C120)</f>
-        <v/>
+      <c r="G120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121" ht="21" customHeight="1">
@@ -4696,13 +4280,11 @@
       <c r="F121" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G121" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C121)</f>
-        <v/>
-      </c>
-      <c r="H121" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C121)</f>
-        <v/>
+      <c r="G121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122" ht="21" customHeight="1">
@@ -4724,13 +4306,11 @@
       <c r="F122" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G122" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C122)</f>
-        <v/>
-      </c>
-      <c r="H122" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C122)</f>
-        <v/>
+      <c r="G122" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123" ht="21" customHeight="1">
@@ -4752,13 +4332,11 @@
       <c r="F123" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G123" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C123)</f>
-        <v/>
-      </c>
-      <c r="H123" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C123)</f>
-        <v/>
+      <c r="G123" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124" ht="21" customHeight="1">
@@ -4780,13 +4358,11 @@
       <c r="F124" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G124" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C124)</f>
-        <v/>
-      </c>
-      <c r="H124" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C124)</f>
-        <v/>
+      <c r="G124" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125" ht="21" customHeight="1">
@@ -4808,13 +4384,11 @@
       <c r="F125" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G125" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C125)</f>
-        <v/>
-      </c>
-      <c r="H125" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C125)</f>
-        <v/>
+      <c r="G125" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126" ht="21" customHeight="1">
@@ -4836,13 +4410,11 @@
       <c r="F126" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G126" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C126)</f>
-        <v/>
-      </c>
-      <c r="H126" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C126)</f>
-        <v/>
+      <c r="G126" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127" ht="21" customHeight="1">
@@ -4864,13 +4436,11 @@
       <c r="F127" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G127" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C127)</f>
-        <v/>
-      </c>
-      <c r="H127" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C127)</f>
-        <v/>
+      <c r="G127" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128" ht="21" customHeight="1">
@@ -4892,13 +4462,11 @@
       <c r="F128" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G128" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C128)</f>
-        <v/>
-      </c>
-      <c r="H128" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C128)</f>
-        <v/>
+      <c r="G128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129" ht="21" customHeight="1">
@@ -4920,13 +4488,11 @@
       <c r="F129" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G129" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C129)</f>
-        <v/>
-      </c>
-      <c r="H129" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C129)</f>
-        <v/>
+      <c r="G129" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130" ht="21" customHeight="1">
@@ -4948,13 +4514,11 @@
       <c r="F130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G130" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C130)</f>
-        <v/>
-      </c>
-      <c r="H130" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C130)</f>
-        <v/>
+      <c r="G130" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131" ht="21" customHeight="1">
@@ -4976,13 +4540,11 @@
       <c r="F131" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G131" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C131)</f>
-        <v/>
-      </c>
-      <c r="H131" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C131)</f>
-        <v/>
+      <c r="G131" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132" ht="21" customHeight="1">
@@ -5004,13 +4566,11 @@
       <c r="F132" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G132" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C132)</f>
-        <v/>
-      </c>
-      <c r="H132" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C132)</f>
-        <v/>
+      <c r="G132" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="H132" s="14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="133" ht="21" customHeight="1">
@@ -5032,13 +4592,11 @@
       <c r="F133" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G133" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C133)</f>
-        <v/>
-      </c>
-      <c r="H133" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C133)</f>
-        <v/>
+      <c r="G133" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134" ht="21" customHeight="1">
@@ -5060,13 +4618,11 @@
       <c r="F134" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G134" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C134)</f>
-        <v/>
-      </c>
-      <c r="H134" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C134)</f>
-        <v/>
+      <c r="G134" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135" ht="21" customHeight="1">
@@ -5088,13 +4644,11 @@
       <c r="F135" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G135" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C135)</f>
-        <v/>
-      </c>
-      <c r="H135" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C135)</f>
-        <v/>
+      <c r="G135" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136" ht="21" customHeight="1">
@@ -5116,13 +4670,11 @@
       <c r="F136" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G136" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C136)</f>
-        <v/>
-      </c>
-      <c r="H136" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C136)</f>
-        <v/>
+      <c r="G136" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137" ht="21" customHeight="1">
@@ -5144,13 +4696,11 @@
       <c r="F137" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G137" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C137)</f>
-        <v/>
-      </c>
-      <c r="H137" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C137)</f>
-        <v/>
+      <c r="G137" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138" ht="21" customHeight="1">
@@ -5172,13 +4722,11 @@
       <c r="F138" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G138" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C138)</f>
-        <v/>
-      </c>
-      <c r="H138" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C138)</f>
-        <v/>
+      <c r="G138" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139" ht="21" customHeight="1">
@@ -5200,13 +4748,11 @@
       <c r="F139" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G139" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C139)</f>
-        <v/>
-      </c>
-      <c r="H139" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C139)</f>
-        <v/>
+      <c r="G139" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140" ht="21" customHeight="1">
@@ -5228,13 +4774,11 @@
       <c r="F140" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G140" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C140)</f>
-        <v/>
-      </c>
-      <c r="H140" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C140)</f>
-        <v/>
+      <c r="G140" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141" ht="21" customHeight="1">
@@ -5256,13 +4800,11 @@
       <c r="F141" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G141" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C141)</f>
-        <v/>
-      </c>
-      <c r="H141" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C141)</f>
-        <v/>
+      <c r="G141" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142" ht="21" customHeight="1">
@@ -5284,13 +4826,11 @@
       <c r="F142" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G142" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C142)</f>
-        <v/>
-      </c>
-      <c r="H142" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C142)</f>
-        <v/>
+      <c r="G142" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143" ht="21" customHeight="1">
@@ -5312,13 +4852,11 @@
       <c r="F143" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G143" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C143)</f>
-        <v/>
-      </c>
-      <c r="H143" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C143)</f>
-        <v/>
+      <c r="G143" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144" ht="21" customHeight="1">
@@ -5340,13 +4878,11 @@
       <c r="F144" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G144" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C144)</f>
-        <v/>
-      </c>
-      <c r="H144" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C144)</f>
-        <v/>
+      <c r="G144" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145" ht="21" customHeight="1">
@@ -5368,13 +4904,11 @@
       <c r="F145" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G145" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C145)</f>
-        <v/>
-      </c>
-      <c r="H145" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C145)</f>
-        <v/>
+      <c r="G145" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146" ht="21" customHeight="1">
@@ -5396,13 +4930,11 @@
       <c r="F146" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G146" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C146)</f>
-        <v/>
-      </c>
-      <c r="H146" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C146)</f>
-        <v/>
+      <c r="G146" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147" ht="21" customHeight="1">
@@ -5424,13 +4956,11 @@
       <c r="F147" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G147" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C147)</f>
-        <v/>
-      </c>
-      <c r="H147" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C147)</f>
-        <v/>
+      <c r="G147" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148" ht="21" customHeight="1">
@@ -5452,13 +4982,11 @@
       <c r="F148" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G148" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C148)</f>
-        <v/>
-      </c>
-      <c r="H148" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C148)</f>
-        <v/>
+      <c r="G148" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149" ht="21" customHeight="1">
@@ -5480,13 +5008,11 @@
       <c r="F149" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G149" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C149)</f>
-        <v/>
-      </c>
-      <c r="H149" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C149)</f>
-        <v/>
+      <c r="G149" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150" ht="21" customHeight="1">
@@ -5508,13 +5034,11 @@
       <c r="F150" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G150" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C150)</f>
-        <v/>
-      </c>
-      <c r="H150" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C150)</f>
-        <v/>
+      <c r="G150" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151" ht="21" customHeight="1">
@@ -5536,13 +5060,11 @@
       <c r="F151" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G151" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C151)</f>
-        <v/>
-      </c>
-      <c r="H151" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C151)</f>
-        <v/>
+      <c r="G151" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152" ht="21" customHeight="1">
@@ -5564,13 +5086,11 @@
       <c r="F152" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G152" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C152)</f>
-        <v/>
-      </c>
-      <c r="H152" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C152)</f>
-        <v/>
+      <c r="G152" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153" ht="21" customHeight="1">
@@ -5592,13 +5112,11 @@
       <c r="F153" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G153" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C153)</f>
-        <v/>
-      </c>
-      <c r="H153" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C153)</f>
-        <v/>
+      <c r="G153" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154" ht="21" customHeight="1">
@@ -5620,13 +5138,11 @@
       <c r="F154" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G154" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C154)</f>
-        <v/>
-      </c>
-      <c r="H154" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C154)</f>
-        <v/>
+      <c r="G154" s="13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H154" s="14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="155" ht="21" customHeight="1">
@@ -5648,13 +5164,11 @@
       <c r="F155" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G155" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C155)</f>
-        <v/>
-      </c>
-      <c r="H155" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C155)</f>
-        <v/>
+      <c r="G155" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156" ht="21" customHeight="1">
@@ -5676,13 +5190,11 @@
       <c r="F156" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G156" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C156)</f>
-        <v/>
-      </c>
-      <c r="H156" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C156)</f>
-        <v/>
+      <c r="G156" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157" ht="21" customHeight="1">
@@ -5704,13 +5216,11 @@
       <c r="F157" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G157" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C157)</f>
-        <v/>
-      </c>
-      <c r="H157" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C157)</f>
-        <v/>
+      <c r="G157" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158" ht="21" customHeight="1">
@@ -5732,13 +5242,11 @@
       <c r="F158" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G158" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C158)</f>
-        <v/>
-      </c>
-      <c r="H158" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C158)</f>
-        <v/>
+      <c r="G158" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159" ht="21" customHeight="1">
@@ -5760,13 +5268,11 @@
       <c r="F159" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G159" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C159)</f>
-        <v/>
-      </c>
-      <c r="H159" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C159)</f>
-        <v/>
+      <c r="G159" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160" ht="21" customHeight="1">
@@ -5788,13 +5294,11 @@
       <c r="F160" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G160" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C160)</f>
-        <v/>
-      </c>
-      <c r="H160" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C160)</f>
-        <v/>
+      <c r="G160" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161" ht="21" customHeight="1">
@@ -5816,13 +5320,11 @@
       <c r="F161" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G161" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C161)</f>
-        <v/>
-      </c>
-      <c r="H161" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C161)</f>
-        <v/>
+      <c r="G161" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162" ht="21" customHeight="1">
@@ -5844,13 +5346,11 @@
       <c r="F162" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G162" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C162)</f>
-        <v/>
-      </c>
-      <c r="H162" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C162)</f>
-        <v/>
+      <c r="G162" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163" ht="21" customHeight="1">
@@ -5872,13 +5372,11 @@
       <c r="F163" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G163" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C163)</f>
-        <v/>
-      </c>
-      <c r="H163" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C163)</f>
-        <v/>
+      <c r="G163" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164" ht="21" customHeight="1">
@@ -5900,13 +5398,11 @@
       <c r="F164" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G164" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C164)</f>
-        <v/>
-      </c>
-      <c r="H164" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C164)</f>
-        <v/>
+      <c r="G164" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165" ht="21" customHeight="1">
@@ -5928,13 +5424,11 @@
       <c r="F165" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G165" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C165)</f>
-        <v/>
-      </c>
-      <c r="H165" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C165)</f>
-        <v/>
+      <c r="G165" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166" ht="21" customHeight="1">
@@ -5956,13 +5450,11 @@
       <c r="F166" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G166" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C166)</f>
-        <v/>
-      </c>
-      <c r="H166" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C166)</f>
-        <v/>
+      <c r="G166" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167" ht="21" customHeight="1">
@@ -5984,13 +5476,11 @@
       <c r="F167" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G167" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C167)</f>
-        <v/>
-      </c>
-      <c r="H167" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C167)</f>
-        <v/>
+      <c r="G167" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168" ht="21" customHeight="1">
@@ -6012,13 +5502,11 @@
       <c r="F168" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G168" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C168)</f>
-        <v/>
-      </c>
-      <c r="H168" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C168)</f>
-        <v/>
+      <c r="G168" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169" ht="21" customHeight="1">
@@ -6040,13 +5528,11 @@
       <c r="F169" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G169" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C169)</f>
-        <v/>
-      </c>
-      <c r="H169" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C169)</f>
-        <v/>
+      <c r="G169" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170" ht="21" customHeight="1">
@@ -6068,13 +5554,11 @@
       <c r="F170" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G170" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C170)</f>
-        <v/>
-      </c>
-      <c r="H170" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C170)</f>
-        <v/>
+      <c r="G170" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171" ht="21" customHeight="1">
@@ -6096,13 +5580,11 @@
       <c r="F171" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G171" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C171)</f>
-        <v/>
-      </c>
-      <c r="H171" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C171)</f>
-        <v/>
+      <c r="G171" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172" ht="21" customHeight="1">
@@ -6124,13 +5606,11 @@
       <c r="F172" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G172" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C172)</f>
-        <v/>
-      </c>
-      <c r="H172" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C172)</f>
-        <v/>
+      <c r="G172" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173" ht="21" customHeight="1">
@@ -6152,13 +5632,11 @@
       <c r="F173" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G173" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C173)</f>
-        <v/>
-      </c>
-      <c r="H173" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C173)</f>
-        <v/>
+      <c r="G173" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174" ht="21" customHeight="1">
@@ -6180,13 +5658,11 @@
       <c r="F174" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G174" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C174)</f>
-        <v/>
-      </c>
-      <c r="H174" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C174)</f>
-        <v/>
+      <c r="G174" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175" ht="21" customHeight="1">
@@ -6208,13 +5684,11 @@
       <c r="F175" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G175" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C175)</f>
-        <v/>
-      </c>
-      <c r="H175" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C175)</f>
-        <v/>
+      <c r="G175" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="176" ht="21" customHeight="1">
@@ -6236,13 +5710,11 @@
       <c r="F176" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G176" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C176)</f>
-        <v/>
-      </c>
-      <c r="H176" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C176)</f>
-        <v/>
+      <c r="G176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177" ht="21" customHeight="1">
@@ -6264,13 +5736,11 @@
       <c r="F177" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G177" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C177)</f>
-        <v/>
-      </c>
-      <c r="H177" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C177)</f>
-        <v/>
+      <c r="G177" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178" ht="21" customHeight="1">
@@ -6292,13 +5762,11 @@
       <c r="F178" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G178" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C178)</f>
-        <v/>
-      </c>
-      <c r="H178" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C178)</f>
-        <v/>
+      <c r="G178" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179" ht="21" customHeight="1">
@@ -6320,13 +5788,11 @@
       <c r="F179" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G179" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C179)</f>
-        <v/>
-      </c>
-      <c r="H179" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C179)</f>
-        <v/>
+      <c r="G179" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180" ht="21" customHeight="1">
@@ -6348,13 +5814,11 @@
       <c r="F180" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G180" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C180)</f>
-        <v/>
-      </c>
-      <c r="H180" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C180)</f>
-        <v/>
+      <c r="G180" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181" ht="21" customHeight="1">
@@ -6376,13 +5840,11 @@
       <c r="F181" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G181" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C181)</f>
-        <v/>
-      </c>
-      <c r="H181" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C181)</f>
-        <v/>
+      <c r="G181" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182" ht="21" customHeight="1">
@@ -6404,13 +5866,11 @@
       <c r="F182" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G182" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C182)</f>
-        <v/>
-      </c>
-      <c r="H182" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C182)</f>
-        <v/>
+      <c r="G182" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183" ht="21" customHeight="1">
@@ -6432,13 +5892,11 @@
       <c r="F183" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G183" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C183)</f>
-        <v/>
-      </c>
-      <c r="H183" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C183)</f>
-        <v/>
+      <c r="G183" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="184" ht="21" customHeight="1">
@@ -6460,13 +5918,11 @@
       <c r="F184" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G184" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C184)</f>
-        <v/>
-      </c>
-      <c r="H184" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C184)</f>
-        <v/>
+      <c r="G184" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="185" ht="21" customHeight="1">
@@ -6488,13 +5944,11 @@
       <c r="F185" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G185" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C185)</f>
-        <v/>
-      </c>
-      <c r="H185" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C185)</f>
-        <v/>
+      <c r="G185" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="186" ht="21" customHeight="1">
@@ -6516,13 +5970,11 @@
       <c r="F186" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G186" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C186)</f>
-        <v/>
-      </c>
-      <c r="H186" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C186)</f>
-        <v/>
+      <c r="G186" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187" ht="21" customHeight="1">
@@ -6544,13 +5996,11 @@
       <c r="F187" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G187" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C187)</f>
-        <v/>
-      </c>
-      <c r="H187" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C187)</f>
-        <v/>
+      <c r="G187" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" s="14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188" ht="21" customHeight="1">
@@ -6572,15 +6022,15 @@
       <c r="F188" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G188" s="13">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$H$80:$H$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C188)</f>
-        <v/>
-      </c>
-      <c r="H188" s="14">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$N$80:$N$757,'[D KLR.xlsx]D KLR'!$A$80:$A$757,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$80:$B$757,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$C$80:$C$757,C188)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="G188" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189"/>
+    <row r="190"/>
     <row r="191">
       <c r="C191" t="inlineStr">
         <is>
